--- a/tables/FST Tables.xlsx
+++ b/tables/FST Tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R_WD\woodbison\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F60847-62FC-4CCC-82F8-EB6E2765A038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DDC1E45-486B-4ADB-9332-0F09E543D0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="20343" windowHeight="12934" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="25">
   <si>
     <t>WBNPGR</t>
   </si>
@@ -79,6 +79,27 @@
   </si>
   <si>
     <t>Temporal Group 2</t>
+  </si>
+  <si>
+    <t>CL</t>
+  </si>
+  <si>
+    <t>ETH</t>
+  </si>
+  <si>
+    <t>NAH</t>
+  </si>
+  <si>
+    <t>NORD</t>
+  </si>
+  <si>
+    <t>AISH</t>
+  </si>
+  <si>
+    <t>Temporal Group 3</t>
+  </si>
+  <si>
+    <t>Wood Buffalo National Park</t>
   </si>
 </sst>
 </file>
@@ -121,11 +142,20 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -153,16 +183,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -183,26 +210,57 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -484,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="1" bestFit="1" customWidth="1"/>
@@ -495,363 +553,1182 @@
     <col min="8" max="8" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="11" max="19" width="8.88671875" style="1"/>
+    <col min="20" max="20" width="14" style="10" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.21875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="5.5546875" style="1" customWidth="1"/>
+    <col min="29" max="29" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.6640625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="6.88671875" style="1" customWidth="1"/>
+    <col min="32" max="32" width="7.6640625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="15" t="s">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="M1" s="15" t="s">
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="T1" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
+      <c r="AH1" s="29"/>
+      <c r="AI1" s="29"/>
+      <c r="AJ1" s="29"/>
+      <c r="AK1" s="29"/>
+    </row>
+    <row r="2" spans="1:37" ht="15.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="M2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="T2" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="U2" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
+      <c r="Y2" s="25"/>
+      <c r="Z2" s="25"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+      <c r="AD2" s="20"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+      <c r="AG2" s="20"/>
+      <c r="AH2" s="20"/>
+      <c r="AI2" s="20"/>
+      <c r="AJ2" s="20"/>
+      <c r="AK2" s="22"/>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A3" s="26"/>
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="M2" s="19" t="s">
+      <c r="K3" s="4"/>
+      <c r="M3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q3" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="T3" s="26"/>
+      <c r="U3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="M3" s="11" t="s">
+      <c r="V3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB3" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD3" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="AF3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="AG3" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH3" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI3" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ3" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK3" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="M4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="T4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="11"/>
+      <c r="AB4" s="11"/>
+      <c r="AC4" s="11"/>
+      <c r="AD4" s="11"/>
+      <c r="AE4" s="11"/>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B5" s="15">
         <v>2.21671993655547E-2</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="M4" s="11" t="s">
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="M5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="16">
+      <c r="N5" s="14">
         <v>6.9421755973056401E-2</v>
       </c>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="T5" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="U5" s="7">
+        <v>-2.1829225145264899E-4</v>
+      </c>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="15"/>
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+      <c r="AH5" s="14"/>
+      <c r="AI5" s="14"/>
+      <c r="AJ5" s="14"/>
+      <c r="AK5" s="11"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B6" s="15">
         <v>9.6456107154438697E-3</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C6" s="15">
         <v>1.07255404018438E-2</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="M5" s="11" t="s">
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="M6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N6" s="14">
         <v>0.120028899158653</v>
       </c>
-      <c r="O5" s="16">
+      <c r="O6" s="14">
         <v>0.10289067348179901</v>
       </c>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="T6" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="U6" s="15">
+        <v>8.8461929590529596E-3</v>
+      </c>
+      <c r="V6" s="7">
+        <v>4.6757178588695504E-3</v>
+      </c>
+      <c r="W6" s="15"/>
+      <c r="X6" s="15"/>
+      <c r="Y6" s="15"/>
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="14"/>
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="14"/>
+      <c r="AH6" s="14"/>
+      <c r="AI6" s="14"/>
+      <c r="AJ6" s="14"/>
+      <c r="AK6" s="11"/>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B7" s="7">
         <v>5.0293664576193898E-3</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C7" s="15">
         <v>7.8595335471503894E-3</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D7" s="7">
         <v>-3.0713570220418898E-3</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="M6" s="11" t="s">
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="M7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="16">
+      <c r="N7" s="14">
         <v>0.199675764891001</v>
       </c>
-      <c r="O6" s="16">
+      <c r="O7" s="14">
         <v>0.17220350501235501</v>
       </c>
-      <c r="P6" s="16">
+      <c r="P7" s="14">
         <v>0.19338842058585101</v>
       </c>
-      <c r="Q6" s="16"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="Q7" s="14"/>
+      <c r="T7" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="U7" s="15">
+        <v>2.2064850436721298E-2</v>
+      </c>
+      <c r="V7" s="15">
+        <v>1.6416417923262299E-2</v>
+      </c>
+      <c r="W7" s="7">
+        <v>2.3229355860284102E-3</v>
+      </c>
+      <c r="X7" s="15"/>
+      <c r="Y7" s="15"/>
+      <c r="Z7" s="15"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="14"/>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="14"/>
+      <c r="AH7" s="14"/>
+      <c r="AI7" s="14"/>
+      <c r="AJ7" s="14"/>
+      <c r="AK7" s="11"/>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B8" s="7">
         <v>8.3294483759851698E-3</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C8" s="15">
         <v>1.4397622452146999E-2</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D8" s="7">
         <v>2.6168096999057899E-3</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E8" s="7">
         <v>-4.0997715550839704E-3</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="M7" s="13" t="s">
+      <c r="F8" s="8"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="M8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="N7" s="18">
+      <c r="N8" s="16">
         <v>5.88708054869602E-2</v>
       </c>
-      <c r="O7" s="18">
+      <c r="O8" s="16">
         <v>6.6752792898197605E-2</v>
       </c>
-      <c r="P7" s="18">
+      <c r="P8" s="16">
         <v>7.6711572196847905E-2</v>
       </c>
-      <c r="Q7" s="18">
+      <c r="Q8" s="16">
         <v>0.19662058371735799</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="T8" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="15">
+        <v>2.2730399762474499E-2</v>
+      </c>
+      <c r="V8" s="15">
+        <v>1.81301844038654E-2</v>
+      </c>
+      <c r="W8" s="7">
+        <v>2.0073662449462499E-3</v>
+      </c>
+      <c r="X8" s="7">
+        <v>1.8360982619247601E-3</v>
+      </c>
+      <c r="Y8" s="15"/>
+      <c r="Z8" s="15"/>
+      <c r="AA8" s="14"/>
+      <c r="AB8" s="14"/>
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="14"/>
+      <c r="AF8" s="14"/>
+      <c r="AG8" s="14"/>
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="14"/>
+      <c r="AJ8" s="14"/>
+      <c r="AK8" s="11"/>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B9" s="14">
         <v>5.2592453143179597E-2</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C9" s="14">
         <v>4.5173068430017199E-2</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D9" s="14">
         <v>4.09339281207984E-2</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E9" s="14">
         <v>5.7552353855091297E-2</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F9" s="14">
         <v>4.9670376854415797E-2</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="T9" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="U9" s="15">
+        <v>5.83931015246546E-2</v>
+      </c>
+      <c r="V9" s="15">
+        <v>5.1699723911771703E-2</v>
+      </c>
+      <c r="W9" s="15">
+        <v>3.7101287046411698E-2</v>
+      </c>
+      <c r="X9" s="15">
+        <v>2.1913816688064101E-2</v>
+      </c>
+      <c r="Y9" s="15">
+        <v>2.76704593874776E-2</v>
+      </c>
+      <c r="Z9" s="15"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="11"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B10" s="14">
         <v>2.2670189257230799E-2</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C10" s="14">
         <v>3.3207367018285201E-2</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D10" s="14">
         <v>2.2686487517314301E-2</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E10" s="14">
         <v>2.7865673545353801E-2</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F10" s="14">
         <v>2.2016677826165801E-2</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G10" s="14">
         <v>5.7179084102334903E-2</v>
       </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="T10" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="U10" s="14">
+        <v>5.96870305426008E-2</v>
+      </c>
+      <c r="V10" s="14">
+        <v>6.6251833140098998E-2</v>
+      </c>
+      <c r="W10" s="14">
+        <v>5.1427027621730098E-2</v>
+      </c>
+      <c r="X10" s="14">
+        <v>4.9876959198804798E-2</v>
+      </c>
+      <c r="Y10" s="14">
+        <v>4.5955360229717801E-2</v>
+      </c>
+      <c r="Z10" s="14">
+        <v>6.7148445609077095E-2</v>
+      </c>
+      <c r="AA10" s="14"/>
+      <c r="AB10" s="14"/>
+      <c r="AC10" s="14"/>
+      <c r="AD10" s="14"/>
+      <c r="AE10" s="14"/>
+      <c r="AF10" s="14"/>
+      <c r="AG10" s="14"/>
+      <c r="AH10" s="14"/>
+      <c r="AI10" s="14"/>
+      <c r="AJ10" s="14"/>
+      <c r="AK10" s="11"/>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B11" s="14">
         <v>0.112230493432023</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C11" s="14">
         <v>0.13643417840521499</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D11" s="14">
         <v>0.106473537395795</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E11" s="14">
         <v>9.12350040305695E-2</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F11" s="14">
         <v>7.6956278453242696E-2</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G11" s="14">
         <v>0.17356668931945601</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H11" s="14">
         <v>0.122157975200926</v>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="T11" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="U11" s="14">
+        <v>9.0113606672190399E-2</v>
+      </c>
+      <c r="V11" s="14">
+        <v>8.7711498045400002E-2</v>
+      </c>
+      <c r="W11" s="14">
+        <v>8.5416128369393302E-2</v>
+      </c>
+      <c r="X11" s="14">
+        <v>8.7228409935301093E-2</v>
+      </c>
+      <c r="Y11" s="14">
+        <v>8.8128162463762802E-2</v>
+      </c>
+      <c r="Z11" s="14">
+        <v>0.110801378410229</v>
+      </c>
+      <c r="AA11" s="14">
+        <v>5.6594152575680998E-2</v>
+      </c>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="14"/>
+      <c r="AD11" s="14"/>
+      <c r="AE11" s="14"/>
+      <c r="AF11" s="14"/>
+      <c r="AG11" s="14"/>
+      <c r="AH11" s="14"/>
+      <c r="AI11" s="14"/>
+      <c r="AJ11" s="14"/>
+      <c r="AK11" s="11"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D12" s="11">
         <v>5.3803028760019697E-3</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E12" s="11">
         <v>8.2385554116385002E-4</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F12" s="11">
         <v>6.8244200092509397E-3</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G12" s="14">
         <v>4.1568198310539498E-2</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H12" s="14">
         <v>2.2531445522091499E-2</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I12" s="14">
         <v>0.122320840230471</v>
       </c>
-      <c r="J11" s="10"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="J12" s="9"/>
+      <c r="T12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="U12" s="14">
+        <v>5.1646193731460698E-2</v>
+      </c>
+      <c r="V12" s="14">
+        <v>5.8544123139827001E-2</v>
+      </c>
+      <c r="W12" s="14">
+        <v>4.44270560808461E-2</v>
+      </c>
+      <c r="X12" s="14">
+        <v>3.9590722025321198E-2</v>
+      </c>
+      <c r="Y12" s="14">
+        <v>3.7863494381881697E-2</v>
+      </c>
+      <c r="Z12" s="14">
+        <v>5.74646480398711E-2</v>
+      </c>
+      <c r="AA12" s="14">
+        <v>1.20556738524914E-2</v>
+      </c>
+      <c r="AB12" s="14">
+        <v>5.8343887450951697E-2</v>
+      </c>
+      <c r="AC12" s="14"/>
+      <c r="AD12" s="14"/>
+      <c r="AE12" s="14"/>
+      <c r="AF12" s="14"/>
+      <c r="AG12" s="14"/>
+      <c r="AH12" s="14"/>
+      <c r="AI12" s="14"/>
+      <c r="AJ12" s="14"/>
+      <c r="AK12" s="11"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B13" s="13">
         <v>8.06479620188842E-3</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C13" s="16">
         <v>1.27724442594827E-2</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D13" s="13">
         <v>1.9728162326586498E-3</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E13" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F13" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G13" s="16">
         <v>5.1045141737721803E-2</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H13" s="16">
         <v>2.3874434670960201E-2</v>
       </c>
-      <c r="I12" s="18">
+      <c r="I13" s="16">
         <v>8.2244836661012705E-2</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J13" s="13">
         <v>5.7159603889417E-3</v>
       </c>
+      <c r="T13" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="U13" s="14">
+        <v>6.7808294875571301E-2</v>
+      </c>
+      <c r="V13" s="14">
+        <v>6.9880078790265407E-2</v>
+      </c>
+      <c r="W13" s="14">
+        <v>6.0223551443473598E-2</v>
+      </c>
+      <c r="X13" s="14">
+        <v>5.0529373388342701E-2</v>
+      </c>
+      <c r="Y13" s="14">
+        <v>5.1899622207066599E-2</v>
+      </c>
+      <c r="Z13" s="14">
+        <v>7.85754135049712E-2</v>
+      </c>
+      <c r="AA13" s="14">
+        <v>3.54643223511307E-2</v>
+      </c>
+      <c r="AB13" s="14">
+        <v>7.75330304495601E-2</v>
+      </c>
+      <c r="AC13" s="14">
+        <v>2.5881586513495699E-2</v>
+      </c>
+      <c r="AD13" s="14"/>
+      <c r="AE13" s="14"/>
+      <c r="AF13" s="14"/>
+      <c r="AG13" s="14"/>
+      <c r="AH13" s="14"/>
+      <c r="AI13" s="14"/>
+      <c r="AJ13" s="14"/>
+      <c r="AK13" s="11"/>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="T14" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="U14" s="14">
+        <v>6.3362386856868097E-2</v>
+      </c>
+      <c r="V14" s="14">
+        <v>6.6459091743746507E-2</v>
+      </c>
+      <c r="W14" s="14">
+        <v>5.8229006349977498E-2</v>
+      </c>
+      <c r="X14" s="14">
+        <v>5.50780533676683E-2</v>
+      </c>
+      <c r="Y14" s="14">
+        <v>5.34917788081503E-2</v>
+      </c>
+      <c r="Z14" s="14">
+        <v>7.7303190307536102E-2</v>
+      </c>
+      <c r="AA14" s="14">
+        <v>2.90783570650897E-2</v>
+      </c>
+      <c r="AB14" s="14">
+        <v>7.0798246240989696E-2</v>
+      </c>
+      <c r="AC14" s="14">
+        <v>2.15507759728472E-2</v>
+      </c>
+      <c r="AD14" s="14">
+        <v>4.1666934710506399E-2</v>
+      </c>
+      <c r="AE14" s="14"/>
+      <c r="AF14" s="14"/>
+      <c r="AG14" s="14"/>
+      <c r="AH14" s="14"/>
+      <c r="AI14" s="14"/>
+      <c r="AJ14" s="14"/>
+      <c r="AK14" s="11"/>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="T15" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="U15" s="14">
+        <v>6.8822505123077707E-2</v>
+      </c>
+      <c r="V15" s="14">
+        <v>6.6397762206805003E-2</v>
+      </c>
+      <c r="W15" s="14">
+        <v>5.2545463641722502E-2</v>
+      </c>
+      <c r="X15" s="14">
+        <v>5.4909850048207802E-2</v>
+      </c>
+      <c r="Y15" s="14">
+        <v>3.7526152465693401E-2</v>
+      </c>
+      <c r="Z15" s="14">
+        <v>8.5799860818918106E-2</v>
+      </c>
+      <c r="AA15" s="14">
+        <v>5.4972864316675599E-2</v>
+      </c>
+      <c r="AB15" s="14">
+        <v>0.11392904168986</v>
+      </c>
+      <c r="AC15" s="14">
+        <v>4.3986360767280699E-2</v>
+      </c>
+      <c r="AD15" s="14">
+        <v>6.4730452751291495E-2</v>
+      </c>
+      <c r="AE15" s="14">
+        <v>7.4313814512347795E-2</v>
+      </c>
+      <c r="AF15" s="14"/>
+      <c r="AG15" s="14"/>
+      <c r="AH15" s="14"/>
+      <c r="AI15" s="14"/>
+      <c r="AJ15" s="14"/>
+      <c r="AK15" s="11"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="T16" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="U16" s="14">
+        <v>6.8421864341672703E-2</v>
+      </c>
+      <c r="V16" s="14">
+        <v>7.2460518224340895E-2</v>
+      </c>
+      <c r="W16" s="14">
+        <v>5.57454534839232E-2</v>
+      </c>
+      <c r="X16" s="14">
+        <v>7.1668725354557303E-2</v>
+      </c>
+      <c r="Y16" s="14">
+        <v>6.0038283839488199E-2</v>
+      </c>
+      <c r="Z16" s="14">
+        <v>8.3151758010144294E-2</v>
+      </c>
+      <c r="AA16" s="14">
+        <v>4.3267236721411702E-2</v>
+      </c>
+      <c r="AB16" s="14">
+        <v>8.9919338782696701E-2</v>
+      </c>
+      <c r="AC16" s="14">
+        <v>3.8178479278530499E-2</v>
+      </c>
+      <c r="AD16" s="14">
+        <v>6.4471199451073893E-2</v>
+      </c>
+      <c r="AE16" s="14">
+        <v>6.8174446007860406E-2</v>
+      </c>
+      <c r="AF16" s="14">
+        <v>7.3788267295981799E-2</v>
+      </c>
+      <c r="AG16" s="14"/>
+      <c r="AH16" s="14"/>
+      <c r="AI16" s="14"/>
+      <c r="AJ16" s="14"/>
+      <c r="AK16" s="11"/>
+    </row>
+    <row r="17" spans="20:37" x14ac:dyDescent="0.25">
+      <c r="T17" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="U17" s="14">
+        <v>0.108822184952613</v>
+      </c>
+      <c r="V17" s="14">
+        <v>9.8425341101753605E-2</v>
+      </c>
+      <c r="W17" s="14">
+        <v>9.1998756302492005E-2</v>
+      </c>
+      <c r="X17" s="14">
+        <v>8.6911049501957299E-2</v>
+      </c>
+      <c r="Y17" s="14">
+        <v>8.3574614561003596E-2</v>
+      </c>
+      <c r="Z17" s="14">
+        <v>0.11405284178236701</v>
+      </c>
+      <c r="AA17" s="14">
+        <v>0.125878664487973</v>
+      </c>
+      <c r="AB17" s="14">
+        <v>0.14810663493848</v>
+      </c>
+      <c r="AC17" s="14">
+        <v>0.129119036373914</v>
+      </c>
+      <c r="AD17" s="14">
+        <v>0.13278554500867901</v>
+      </c>
+      <c r="AE17" s="14">
+        <v>0.13692118663747599</v>
+      </c>
+      <c r="AF17" s="14">
+        <v>0.129688127840448</v>
+      </c>
+      <c r="AG17" s="14">
+        <v>0.147779674950511</v>
+      </c>
+      <c r="AH17" s="14"/>
+      <c r="AI17" s="14"/>
+      <c r="AJ17" s="14"/>
+      <c r="AK17" s="11"/>
+    </row>
+    <row r="18" spans="20:37" x14ac:dyDescent="0.25">
+      <c r="T18" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="U18" s="14">
+        <v>0.18602971375798599</v>
+      </c>
+      <c r="V18" s="14">
+        <v>0.17736293458893301</v>
+      </c>
+      <c r="W18" s="14">
+        <v>0.160981448498943</v>
+      </c>
+      <c r="X18" s="14">
+        <v>0.15239407268145</v>
+      </c>
+      <c r="Y18" s="14">
+        <v>0.13129495563809901</v>
+      </c>
+      <c r="Z18" s="14">
+        <v>0.22015450046853599</v>
+      </c>
+      <c r="AA18" s="14">
+        <v>0.21591773668511899</v>
+      </c>
+      <c r="AB18" s="14">
+        <v>0.26649513451768603</v>
+      </c>
+      <c r="AC18" s="14">
+        <v>0.21337196862641999</v>
+      </c>
+      <c r="AD18" s="14">
+        <v>0.209364374347941</v>
+      </c>
+      <c r="AE18" s="14">
+        <v>0.20456960656131401</v>
+      </c>
+      <c r="AF18" s="14">
+        <v>0.19183076960658799</v>
+      </c>
+      <c r="AG18" s="14">
+        <v>0.21197060881285901</v>
+      </c>
+      <c r="AH18" s="14">
+        <v>0.20061643459746001</v>
+      </c>
+      <c r="AI18" s="14"/>
+      <c r="AJ18" s="14"/>
+      <c r="AK18" s="11"/>
+    </row>
+    <row r="19" spans="20:37" x14ac:dyDescent="0.25">
+      <c r="T19" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="U19" s="16">
+        <v>0.155248435123476</v>
+      </c>
+      <c r="V19" s="16">
+        <v>0.148592665517289</v>
+      </c>
+      <c r="W19" s="16">
+        <v>0.126233171663067</v>
+      </c>
+      <c r="X19" s="16">
+        <v>0.114393576510607</v>
+      </c>
+      <c r="Y19" s="16">
+        <v>0.10338759093696601</v>
+      </c>
+      <c r="Z19" s="16">
+        <v>0.14770455169899099</v>
+      </c>
+      <c r="AA19" s="16">
+        <v>0.195520114466116</v>
+      </c>
+      <c r="AB19" s="16">
+        <v>0.225597816917288</v>
+      </c>
+      <c r="AC19" s="16">
+        <v>0.17669149031254</v>
+      </c>
+      <c r="AD19" s="16">
+        <v>0.18784539760389399</v>
+      </c>
+      <c r="AE19" s="16">
+        <v>0.18825429596873</v>
+      </c>
+      <c r="AF19" s="16">
+        <v>0.14462225002304399</v>
+      </c>
+      <c r="AG19" s="16">
+        <v>0.20625558380338199</v>
+      </c>
+      <c r="AH19" s="16">
+        <v>0.162512522901646</v>
+      </c>
+      <c r="AI19" s="16">
+        <v>0.14988751081628199</v>
+      </c>
+      <c r="AJ19" s="16"/>
+      <c r="AK19" s="13"/>
+    </row>
+    <row r="20" spans="20:37" x14ac:dyDescent="0.25">
+      <c r="T20" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="U20" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="V20" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="W20" s="14">
+        <v>6.8453153595735804E-3</v>
+      </c>
+      <c r="X20" s="14">
+        <v>1.9493689197702599E-2</v>
+      </c>
+      <c r="Y20" s="14">
+        <v>2.1158199947075899E-2</v>
+      </c>
+      <c r="Z20" s="14">
+        <v>5.4430073378405899E-2</v>
+      </c>
+      <c r="AA20" s="14">
+        <v>6.2257972266753898E-2</v>
+      </c>
+      <c r="AB20" s="14">
+        <v>8.5391274880242798E-2</v>
+      </c>
+      <c r="AC20" s="14">
+        <v>5.4959918427446797E-2</v>
+      </c>
+      <c r="AD20" s="14">
+        <v>6.7867199846518206E-2</v>
+      </c>
+      <c r="AE20" s="14">
+        <v>6.4177757099114899E-2</v>
+      </c>
+      <c r="AF20" s="14">
+        <v>6.7535103837508506E-2</v>
+      </c>
+      <c r="AG20" s="14">
+        <v>6.9614871907789505E-2</v>
+      </c>
+      <c r="AH20" s="14">
+        <v>0.101533663532932</v>
+      </c>
+      <c r="AI20" s="14">
+        <v>0.17928639646774</v>
+      </c>
+      <c r="AJ20" s="14">
+        <v>0.15351338736055001</v>
+      </c>
+      <c r="AK20" s="11"/>
+    </row>
+    <row r="21" spans="20:37" x14ac:dyDescent="0.25">
+      <c r="T21" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="U21" s="16">
+        <v>2.1192519788563E-2</v>
+      </c>
+      <c r="V21" s="16">
+        <v>1.6767484366416601E-2</v>
+      </c>
+      <c r="W21" s="13">
+        <v>1.85467783261783E-3</v>
+      </c>
+      <c r="X21" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y21" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z21" s="13">
+        <v>1.27249282890371E-2</v>
+      </c>
+      <c r="AA21" s="16">
+        <v>4.3765343192786098E-2</v>
+      </c>
+      <c r="AB21" s="16">
+        <v>8.0701868419587305E-2</v>
+      </c>
+      <c r="AC21" s="16">
+        <v>3.54998683213891E-2</v>
+      </c>
+      <c r="AD21" s="16">
+        <v>4.8148113590241001E-2</v>
+      </c>
+      <c r="AE21" s="16">
+        <v>5.0800263237535198E-2</v>
+      </c>
+      <c r="AF21" s="16">
+        <v>4.3513848103225401E-2</v>
+      </c>
+      <c r="AG21" s="16">
+        <v>6.0422632657162099E-2</v>
+      </c>
+      <c r="AH21" s="16">
+        <v>8.1159039956357801E-2</v>
+      </c>
+      <c r="AI21" s="16">
+        <v>0.138333180432958</v>
+      </c>
+      <c r="AJ21" s="16">
+        <v>0.108582226693951</v>
+      </c>
+      <c r="AK21" s="13">
+        <v>1.95329772235724E-2</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="8">
+    <mergeCell ref="A2:A3"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="U2:Z2"/>
+    <mergeCell ref="T1:AK1"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="M2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>